--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260609.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260609.xlsx
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,000,822</t>
+          <t>1,725,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,725,000</t>
+          <t>1,000,822</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>798,897</t>
+          <t>5,606,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>562,000</t>
+          <t>798,897</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,606,000</t>
+          <t>562,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>778,000</t>
+          <t>1,534,384</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,534,384</t>
+          <t>778,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>937,659</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>370,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>370,000</t>
+          <t>937,659</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>5,011,956</t>
+          <t>828,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>828,000</t>
+          <t>5,011,956</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,186,076</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>202606WVHFM6F</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>202606WVHFM6F</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>269</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>90,000</t>
+          <t>1,186,076</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
